--- a/Result/checksun_type/螺絲螺帽.xlsx
+++ b/Result/checksun_type/螺絲螺帽.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>34.04000000000001</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>33.7</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>33.7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>20544.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>12325.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>12325</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>15227.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>10239.48</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>10239.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>369.9186995674609</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>20544</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>20544.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>33.93</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>33.76</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>33.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>4244.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>10846.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>10846.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>17226.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>10216.08</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>10216.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-250.436468096339</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>4244</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>4244.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>33.89</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>33.74</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>33.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>19679.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>12730.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>12730.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>17237.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>11234.76</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>11234.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>618.7145948159596</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>19679</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>19679.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>33.81</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>33.71</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>33.71</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>33.69</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>9167.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>13290.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>13290.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>17298.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>10984.62</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>10984.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>184.5120205901003</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>9167</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>9167.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>33.91</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.71</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.71</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>33.69</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>7991.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>15581.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>15581</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>16546.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>10935.12</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>10935.12</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>683.9186281035109</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>7991</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>7991.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>33.9</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.7</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>33.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>13150.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>18129.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>18129.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>16550.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>12000.38</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>12000.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1498.930973547544</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>13150</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>13150.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>33.93</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>33.69</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>13664.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>23607.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>23607</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>16207.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>11919.3</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>11919.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>2056.951075126608</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>13664</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>13664.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>33.88</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.68</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.68</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>33.69</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>22482.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>21744.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>21744.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>15368.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>11725.96</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>11725.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>2725.588681842177</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>22482</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>22482.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>33.87</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>33.68</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>33.68</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>20618.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>21306.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>21306</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>13978.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>11418.06</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>11418.06</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>2638.657095655772</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>20618</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>20618.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>33.79</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>33.68</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>33.68</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>20732.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>17512.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>17512.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>12926.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>11146.18</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>11146.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>2619.945647687488</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>20732</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>20732.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>33.77999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>33.69</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>33.69</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>40539.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>14972.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>14972</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>12093.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>10852.0</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>10852</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>2487.431234601099</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>40539</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>40539.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>45.17</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>43.67</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>45.4</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>43.67</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>45.4</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>13215.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>6892.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>6892.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>8025.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>6026.98</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>6026.98</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>226.292776275056</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>13215</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>13215.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>44.68000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>43.52</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>45.46</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>45.46</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>4678.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>5761.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>5761.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>7164.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>5833.6</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>5833.6</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-378.8892105045425</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>4678</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>4678.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>44.08</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>43.49</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>45.56</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>45.56</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2898.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>6179.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>6179</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>7014.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>5800.5</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>5800.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-315.2245769573792</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2898</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2898.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>43.77</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>45.66</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>45.66</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>3577.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>6384.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>6384.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>7100.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>5793.34</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>5793.34</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-22.30279414152574</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>3577</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>3577.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>43.59</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>43.48</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>45.77</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>45.77</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>10096.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>6153.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>6153.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>7088.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>5764.8</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>5764.8</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>324.203423957606</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>10096</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>10096.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>43.32000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>43.43</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>45.86</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>45.86</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>7557.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>9157.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>9157.200000000001</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>6679.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5677.98</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5677.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>109.1693275293092</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>7557</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>7557.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>43.17</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>43.48</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>45.99</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>45.99</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>6767.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>8568.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>8568.200000000001</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>6711.8</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5623.9</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5623.9</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>70.11457093426543</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>6767</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>6767.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>43.33</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>43.67</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>46.18</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>43.67</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>46.18</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>3925.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>7850.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>7850.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>6301.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5748.56</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5748.56</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>96.46082683655095</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>3925</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>3925.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>43.46</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>43.81</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>46.3</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>43.81</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>46.3</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>2423.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>7817.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>7817.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>6289.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5756.82</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5756.82</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>435.1533057385113</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>2423</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2423.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>43.48999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>43.94</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>46.4</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>25114.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>8024.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>8024</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>6805.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>5842.78</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>5842.78</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>1064.387086107794</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>25114</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>25114.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>43.67</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>44.08</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>46.5</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>44.08</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>46.5</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>4612.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>4201.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>4201.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>5928.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>5418.18</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>5418.18</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-505.8999092970807</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>4612</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>4612.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>29.11</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>28.96</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>233900.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>0</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>19571.5078498181</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>233900</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>233900.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>29.04</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>28.76</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>28.96</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>150772.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>0</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>29531.71991090605</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>150772</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>150772.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>28.89</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>28.73</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>28.96</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>819650.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>0</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>51612.46142992791</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>819650</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>819650.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>28.77</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>28.98</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>511490.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>0</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>9647.575691747421</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>511490</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>511490.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>28.75</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>28.98</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>0</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-28690.29334257476</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>0</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>28.78</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>28.75</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>28.99</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>28.99</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>57350.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>169795.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>169795.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>112548.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-28690.29334257476</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>57350</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>57350.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>28.8</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>28.73</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>29</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>285299.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>169905.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>169905.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>191209.3</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-21741.36084621283</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>285299</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>285299.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>28.82</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>28.73</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>29.02</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>148409.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>118728.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>118728</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>182534.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-35460.9443926168</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>148409</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>148409.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>28.89</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>28.73</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>29.04</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>29.04</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>222491.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>94846.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>94846.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>170684.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-39127.10144488615</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>222491</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>222491.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>28.91</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>28.73</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>29.04</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>29.04</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>135427.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>59411.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>59411.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>176834.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-50904.42932509637</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>135427</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>135427.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>28.93</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>29.04</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>29.04</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>57900.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>55301.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>55301.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>177828.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-56582.88239235754</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>57900</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>57900.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>26.75</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>27.65</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>28.62</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>28.62</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>637.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>410.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>410.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>934.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>956.24</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>956.24</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-93.40117596835648</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>637</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>637.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>26.52</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>27.69</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>28.66</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>28.66</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>11.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1014.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1014.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>906.4</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>956.08</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>956.08</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-95.76765529898591</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>11</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>26.72</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>27.77</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>28.74</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>28.74</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>377.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1201.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1201.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>955.0</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>965.16</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>965.16</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-28.65663808206421</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>377</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>377.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>26.97</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>27.87</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>28.82</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>513.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1222.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1222.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>989.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>977.96</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>977.96</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>29.02540930218356</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>513</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>513.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>27.26</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>27.99</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>28.89</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>28.89</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>514.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1351.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1351.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1185.6</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>1025.66</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>1025.66</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>95.82028380460247</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>514</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>514.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>27.47</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>28.09</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>28.96</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>3657.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1459.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1459.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1267.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>1024.34</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>1024.34</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>187.7122372436079</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>3657</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>3657.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>27.75</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>28.21</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>29.04</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>29.04</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>798.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>798.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>953.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>957.54</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>957.54</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-24.46755203079886</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>947</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>947.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>27.81</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>28.28</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>29.1</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>481.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>708.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>708.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>887.5</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>957.82</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>957.8200000000001</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-36.35055270742293</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>481</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>481.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>27.83</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>28.34</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>29.15</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>1160.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>757.2</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>757.2</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>857.0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>967.52</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>967.52</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-2.099462505906558</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>1160</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1160.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>27.88</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>29.2</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1052.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1019.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1019.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>878.9</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>955.78</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>955.78</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-25.84435284281506</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1052</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1052.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>27.95</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>29.27</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>29.27</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>352.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1076.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1076.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>866.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>961.24</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>961.24</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-47.27118357972665</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>352</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>352.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>10.12</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>10.86</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>10.86</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>1382.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>826.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>826.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>1180.8</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>1607.8</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>1607.8</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-80.50831654224248</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>1382</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>1382.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>10.12</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>10.64</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>10.89</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>10.89</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>1116.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>766.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>766</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>1140.6</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1605.7</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1605.7</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-121.4751372260237</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>1116</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>1116.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>10.15</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>10.69</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>10.92</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>10.92</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>324.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>879.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>879.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>1133.0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1608.84</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1608.84</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-147.1607690162102</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>324</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>324.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>10.13</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>10.75</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>10.96</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>10.96</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>726.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1399.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>1399.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>1286.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1739.64</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1739.64</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-93.74164410875483</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>726</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>726.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>10.25</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>11</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>586.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>1394.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>1394</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>1346.7</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1741.14</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1741.14</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-57.15212123707738</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>586</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>586.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>10.38</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>10.84</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>11.05</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1078.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1534.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1534.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>1351.5</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1739.62</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1739.62</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>12.15977290950013</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1078</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1078.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>10.49</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>10.88</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>11.09</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1682.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>1515.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>1515.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>1731.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1729.68</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1729.68</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>58.02820122927187</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1682</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1682.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>10.55</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>10.91</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>11.14</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>11.14</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>2926.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>1386.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>1386.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>1628.1</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1711.18</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1711.18</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>56.76780592790033</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>2926</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>2926.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>10.68</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>10.96</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>11.18</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>11.18</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>698.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>1173.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>1173.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>1400.9</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1677.58</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1677.58</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-80.34589471434106</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>698</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>698.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>10.76</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>11.22</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>11.22</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>1290.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>1299.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>1299.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>1436.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1689.04</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1689.04</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-34.63882796345956</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>1290</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>1290.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>10.8</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>10.98</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>11.25</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>980.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>1168.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>1168.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>1514.9</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1682.36</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1682.36</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-31.53448874921946</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>980</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>980.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>53.34</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>51.78</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>51.67</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>51.78</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>51.67</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>2449221.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>12808622.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>12808622.4</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>13226048.6</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>5670478.74</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>5670478.74</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>1904173.062620861</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>2449221</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>2449221.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>53.1</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>51.66</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>51.64</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>51.64</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>54812475.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>13716163.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>13716163.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>13106992.6</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>5665684.36</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>5665684.36</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>3315675.505646704</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>54812475</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>54812475.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>52.58000000000001</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>51.54</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>51.61</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>51.61</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>1939839.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>4131975.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>4131975.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>7912217.7</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>4597832.22</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>4597832.22</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-396658.0580894761</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>1939839</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>1939839.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>52.12</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>51.45</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>51.59</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>51.59</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>3398754.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>4125669.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>4125669.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>7829777.3</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>4569706.76</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>4569706.76</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-20900.07563796453</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>3398754</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>3398754.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>51.78000000000001</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>51.36</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>51.57</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>51.57</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>1442823.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>13612188.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>13612188.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>7563388.7</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>4533015.6</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>4533015.6</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>360331.1519941222</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>1442823</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1442823.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>51.5</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>51.56</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>51.56</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>6986926.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>13643474.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>13643474.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>10254232.5</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>4539513.64</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>4539513.64</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>1101642.257468741</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>6986926</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>6986926.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>51.18</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>51.25</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>51.54</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>51.54</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>6891535.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>12497821.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>12497821.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>10304360.8</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>4427999.56</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>4427999.56</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>1527302.720380027</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>6891535</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>6891535.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>51.16</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>51.24</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>51.55</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>51.55</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>1908310.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>11692460.0</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>11692460</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>9784858.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>4303102.64</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>4303102.64</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>2091063.034525434</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>1908310</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>1908310.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>51.16</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>51.25</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>51.56</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>51.56</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>50831348.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>11533885.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>11533885</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>9830585.2</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>4300279.86</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>4300279.86</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>3355671.053500108</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>50831348</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>50831348.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>51.16</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>51.26</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>51.56</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>51.56</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>1599255.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>1514589.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>1514589</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>4978430.7</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>3325504.7</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>3325504.7</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-199345.5284467889</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1599255</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1599255.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>51.14</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>51.26</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>51.58</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>51.58</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>1258661.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>6864990.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>6864990.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>4926666.4</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>3300804.76</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>3300804.76</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>4045.944787886925</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>1258661</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>1258661.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>104.1</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>106.6</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>120.39</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>120.39</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>100616146.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>39907180.8</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>39907180.8</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>36360390.4</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>112974230.9</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>112974230.9</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-2610721.237659656</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>100616146</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>100616146.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>102.2</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>106.78</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>120.78</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>106.78</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>120.78</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>16101964.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>23892723.2</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>23892723.2</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>31881531.4</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>114373076.4</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>114373076.4</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-9014048.464080215</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>16101964</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>16101964.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>101.3</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>107.18</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>121.38</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>107.18</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>121.38</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>18893555.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>30919847.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>30919847.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>33527582.9</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>119381609.48</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>119381609.48</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-8784637.556678154</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>18893555</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>18893555.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>101.4</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>107.8</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>122.02</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>122.02</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>43195246.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>37832948.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>37832948.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>34101036.3</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>123228555.26</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>123228555.26</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-8442269.669079557</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>43195246</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>43195246.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>103.0</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>108.8</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>122.72</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>122.72</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>20728993.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>32673934.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>32673934.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>34713594.3</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>127360637.74</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>127360637.74</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-10255415.66290016</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>20728993</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>20728993.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>104.2</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>109.55</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>123.41</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>123.41</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>20543858.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>32813600.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>32813600</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>37104210.8</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>135685366.26</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>135685366.26</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-10072260.84468315</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>20543858</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>20543858.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>106.0</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>110.48</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>124.17</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>110.48</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>124.17</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>51237586.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>39870339.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>39870339.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>37806102.3</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>152890945.5</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>152890945.5</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-9431051.609920166</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>51237586</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>51237586.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>107.1</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>111.48</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>125.16</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>111.48</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>125.16</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>53459061.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>36135318.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>36135318.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>37811717.0</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>214011460.78</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>214011460.78</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-11466828.85990447</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>53459061</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>53459061.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>107.7</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>112.32</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>125.99</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>112.32</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>125.99</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>17400174.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>30369123.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>30369123.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>39612637.6</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>232296578.54</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>232296578.54</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-14203567.65059974</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>17400174</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>17400174.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>107.4</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>113.1</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>126.49</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>126.49</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>21427321.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>36753254.2</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>36753254.2</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>61015817.9</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>239918216.68</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>239918216.68</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-13742472.04264299</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>21427321</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>21427321.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>107.1</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>113.78</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>127.06</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>113.78</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>127.06</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>55827556.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>41394821.6</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>41394821.6</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>65530420.1</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>258668693.84</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>258668693.84</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-13024441.49403896</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>55827556</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>55827556.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>29.19</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>29.07</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>29.62</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>29.62</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>1856.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>1070.0</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>1070</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>1407.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>1520.08</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>1520.08</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-47.13498287806874</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>1856</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>1856.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>29.07</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>29.07</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>29.64</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>29.64</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>472.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>931.2</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>931.2</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>1424.0</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>1553.8</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>1553.8</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-113.7377666337018</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>472</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>472.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>29.01</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>29.67</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>29.67</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>1479.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>1139.6</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>1139.6</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>1524.3</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>1617.06</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>1617.06</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-56.53682319054542</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>1479</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>1479.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>28.99</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>29.07</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>29.72</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>29.72</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>1223.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>1022.4</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>1022.4</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>1553.4</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>1621.62</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>1621.62</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-80.694874586374</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>1223</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>1223.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>29.01</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>29.08</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>29.78</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>29.78</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>320.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>1227.8</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>1227.8</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>1585.4</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>1625.54</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>1625.54</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-84.8958453451869</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>320</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>29.09</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>29.84</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>1162.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>1745.2</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>1745.2</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>1599.6</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>1643.1</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>1643.1</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>8.88476233312258</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>1162</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>1162.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>29.12</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>29.9</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>29.9</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>1514.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1916.8</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1916.8</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>1748.8</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>1641.9</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>1641.9</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>52.32546036166696</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>1514</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>1514.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>29.15</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>29.96</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>29.96</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>893.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1909.0</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1909</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>1644.9</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>1630.4</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>1630.4</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>74.80054824667127</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>893</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>893.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>29.1</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>30.01</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>30.01</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>2250.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>2084.4</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>2084.4</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>1751.0</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>1645.84</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>1645.84</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>170.7720827878679</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>2250</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>2250.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>29.12</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>30.06</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>30.06</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>2907.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>1943.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>1943</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>1572.1</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>1636.22</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>1636.22</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>156.3824148900105</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>2907</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>2907.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>29.0</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>30.11</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>30.11</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>2020.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1454.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1454</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>1332.7</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>1612.82</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>1612.82</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>59.84780307557139</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>2020</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>2020.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>25.02</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>25.32</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>331.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>485.2</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>485.2</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>640.4</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>757.72</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>757.72</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-41.27741637364784</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>331</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>331.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>26.04</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>26.04</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>681.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>648.0</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>648</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>630.6</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>756.16</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>756.16</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-22.43691546251989</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>681</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>681.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>25.05</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>25.38</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>26.09</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>26.09</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>499.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>581.2</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>581.2</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>622.2</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>757.3</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>757.3</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-32.22059575153276</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>499</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>499.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>25.09</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>25.41</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>26.15</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>456.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>600.8</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>600.8</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>638.6</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>760.92</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>760.92</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-25.54654631613914</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>456</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>456.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>25.19</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>26.21</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>26.21</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>459.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>743.2</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>743.2</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>694.2</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>756.98</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>756.98</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-10.49267046857199</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>459</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>459.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>25.28</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>25.46</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>26.28</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>26.28</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>1145.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>795.6</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>795.6</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>704.6</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>761.76</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>761.76</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>11.06617611611568</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>1145</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>1145.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>25.38</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>26.33</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>26.33</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>347.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>613.2</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>613.2</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>624.1</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>754.88</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>754.88</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-32.03069219562019</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>347</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>347.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>25.33</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>26.38</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>26.38</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>597.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>663.2</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>663.2</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>647.3</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>753.46</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>753.46</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-6.953693633970602</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>597</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>597.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>25.33</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>25.59</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>26.42</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>26.42</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>1168.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>676.4</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>676.4</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>613.5</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>754.24</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>754.24</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>2.333221941027773</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>1168</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>1168.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>25.28</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>26.46</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>721.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>645.2</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>645.2</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>589.5</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>737.22</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>737.22</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-45.66165659258274</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>721</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>721.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>25.21</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>25.66</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>26.51</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>26.51</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>233.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>613.6</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>613.6</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>555.2</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>742.34</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>742.34</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-64.70213819086268</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>233</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>233.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>7.984</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>7.89</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>7.85</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>7.85</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>10795494.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>4215428.6</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>4215428.6</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>4358568.5</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>3099314.18</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>3099314.18</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>533524.1449098522</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>10795494</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>10795494.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>7.895999999999999</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>7.86</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>7.84</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>7.84</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>2236826.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>2539862.6</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>2539862.6</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>3593500.8</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>2943078.04</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>2943078.04</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-58227.44031554088</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>2236826</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>2236826.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>7.897999999999999</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>7.86</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>7.84</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>7.84</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>2067960.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>2935892.4</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>2935892.4</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>3671464.1</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>2985148.54</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>2985148.54</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>15492.84651659615</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>2067960</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>2067960.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>7.938</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>7.85</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>7.85</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>7.85</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>3635100.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>4006522.2</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>4006522.2</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>3602255.5</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>2994366.32</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>2994366.32</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>138347.0117583419</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>3635100</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>3635100.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>7.984</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>7.85</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>7.86</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>7.86</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>2341763.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>4281698.8</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>4281698.8</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>3428143.9</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>2983496.5</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>2983496.5</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>141004.1402551807</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>2341763</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>2341763.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>7.981999999999999</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>7.85</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>7.86</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>7.86</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>2417664.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>4501708.4</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>4501708.4</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>3436908.1</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>2969715.06</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>2969715.06</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>278335.997384408</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>2417664</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>2417664.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>7.976000000000001</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>7.85</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>7.87</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>7.87</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>4216975.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>4647139.0</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>4647139</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>3343790.2</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>3493993.26</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>3493993.26</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>456451.5433767182</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>4216975</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>4216975.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>7.936</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>7.85</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>7.87</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>7.87</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>7421109.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>4407035.8</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>4407035.8</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>3187929.2</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>3433413.24</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>3433413.24</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>501817.1611022786</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>7421109</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>7421109.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>7.868</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>7.84</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>7.88</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>5010983.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>3197988.8</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>3197988.8</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>2609668.7</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>3330523.12</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>3330523.12</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>205403.0735279988</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>5010983</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>5010983.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>7.828</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>7.83</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>7.88</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>3441811.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>2574589.0</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>2574589</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>2309858.2</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>3277405.46</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>3277405.46</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>32846.33865302708</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>3441811</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>3441811.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,21 +47927,17 @@
           <t>7.806</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>7.83</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
+      <c r="AM111" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AO111" t="inlineStr">
         <is>
           <t>7.89</t>
         </is>
       </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>7.89</t>
-        </is>
-      </c>
       <c r="AP111" t="inlineStr">
         <is>
           <t>18.37</t>
@@ -48636,20 +47978,16 @@
           <t>3144817.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>2372107.8</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>2372107.8</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>2257015.4</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>3272974.46</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>3272974.46</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-46710.79469168372</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>3144817</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>3144817.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>8.459999999999999</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>8.68</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>9.06</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>9.06</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>3737926.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>2293923.6</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>2293923.6</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>2665931.6</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>3501500.12</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>3501500.12</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-194853.3927038419</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>3737926</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>3737926.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>8.392</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>8.68</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>9.07</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>9.07</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>2147583.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>2152763.6</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>2152763.6</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>2767202.3</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>3485690.08</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>3485690.08</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-334331.4059387725</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>2147583</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>2147583.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>8.424000000000001</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>9.1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>1240045.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>2238085.4</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>2238085.4</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>2732103.5</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>3533987.4</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>3533987.4</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-351251.4103480033</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>1240045</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>1240045.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>8.478</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>8.73</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>9.13</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>9.130000000000001</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>2827352.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>2456676.8</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>2456676.8</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>2769527.2</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>3551150.54</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>3551150.54</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>-265641.9377059042</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>2827352</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>2827352.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>8.592</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>8.76</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>9.16</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>9.16</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>1516712.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>2607787.4</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>2607787.4</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>2824589.2</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>3526108.82</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>3526108.82</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>-303924.0861562658</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>1516712</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>1516712.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>8.704</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>8.79</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>9.19</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>9.19</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>3032126.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>3037939.6</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>3037939.6</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>3003854.9</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>3535828.66</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>3535828.66</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>-207332.7237226302</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>3032126</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>3032126.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>8.814</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>8.82</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>9.22</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>9.220000000000001</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>2574192.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>3381641.0</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>3381641</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>3529049.4</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>3523707.72</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>3523707.72</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>-224306.1086844858</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>2574192</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>2574192.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>8.848</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>8.84</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>9.25</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>9.25</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>2333002.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>3226121.6</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>3226121.6</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>3565981.8</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>3525734.58</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>3525734.58</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>-191478.5118912617</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>2333002</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>2333002.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>8.874</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>8.86</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>9.27</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>9.27</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>3582905.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>3082377.6</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>3082377.6</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>3607678.5</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>3513884.48</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>3513884.48</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>-111901.6410476821</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>3582905</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>3582905.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>8.866</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>8.87</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>9.29</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>9.289999999999999</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>3667473.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>3041391.0</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>3041391</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>3424701.9</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>3484834.32</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>3484834.32</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>-128142.0883765803</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>3667473</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>3667473.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>8.854</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>8.88</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>9.31</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>9.31</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>4750633.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>2969770.2</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>2969770.2</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>3585229.3</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>3456014.58</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>3456014.58</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>-155827.0814044145</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>4750633</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>4750633.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53087,11 @@
           <t>15.16</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>15.42</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>16.16</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>16.16</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53138,16 @@
           <t>759015.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>822662.8</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>822662.8</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>899025.8</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>839437.72</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>839437.72</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>-27651.22974182363</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>759015</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>759015.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53517,11 @@
           <t>15.09</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>16.2</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53568,16 @@
           <t>610121.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>888460.4</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>888460.4</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>911030.7</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>833228.32</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>833228.3199999999</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>-24939.23107736837</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>610121</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>610121.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53947,11 @@
           <t>15.14</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>16.25</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53998,16 @@
           <t>328107.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>1019582.4</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>1019582.4</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>881008.0</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>833631.48</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>833631.48</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>-4221.331875383272</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>328107</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>328107.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>15.21</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>15.53</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>16.3</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>1370613.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>1039667.4</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>1039667.4</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>976340.4</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>832143.12</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>832143.12</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>55742.21455157339</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>1370613</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>1370613.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>15.29</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>16.35</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>16.35</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>1045458.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>969620.4</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>969620.4</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>895996.7</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>815201.94</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>815201.9399999999</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>27716.55892752646</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>1045458</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>1045458.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>15.34</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>16.4</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>1088003.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>975388.8</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>975388.8</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>889500.6</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>803125.26</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>803125.26</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>21528.0666457623</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>1088003</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>1088003.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>15.38</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>15.64</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>16.45</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>16.45</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>1265731.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>933601.0</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>933601</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>848828.0</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>789392.84</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>789392.84</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>7360.111005893559</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>1265731</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>1265731.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>15.4</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>16.49</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>16.49</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>428532.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>742433.6</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>742433.6</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>764703.6</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>770458.0</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>770458</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>-32184.97244412953</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>428532</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>428532.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>15.43</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>15.7</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>16.53</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>1020378.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>913013.4</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>913013.4</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>789901.6</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>831542.84</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>831542.84</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>2171.407357413555</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>1020378</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>1020378.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>15.47</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>15.75</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>16.58</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>16.58</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>1074300.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>822373.0</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>822373</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>741812.3</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>839169.14</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>839169.14</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>-12237.67176028958</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>1074300</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>1074300.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>15.51</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>15.8</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>16.62</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>16.62</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>879064.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>803612.4</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>803612.4</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>728036.7</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>823720.16</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>823720.16</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>-38162.36793699802</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>879064</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>879064.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
